--- a/4_outputs/final/Table26.xlsx
+++ b/4_outputs/final/Table26.xlsx
@@ -420,15 +420,15 @@
   <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="7" customWidth="1" min="7" max="7"/>
-    <col width="7" customWidth="1" min="8" max="8"/>
-    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -439,61 +439,69 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Semantic gaps</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr"/>
+          <t>Full Corpus</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr"/>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Curated AI/SDG</t>
+        </is>
+      </c>
       <c r="E1" s="1" t="inlineStr"/>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Coverage predictors</t>
+          <t>SDGi VNR/VLR</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr"/>
-      <c r="H1" s="1" t="inlineStr"/>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>UNGDC</t>
+        </is>
+      </c>
       <c r="I1" s="1" t="inlineStr"/>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pol.% (n)</t>
+        </is>
+      </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Raw</t>
+          <t>sem. (n)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Adj.</t>
+          <t>pol.% (n)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Reg.</t>
+          <t>sem. (n)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cov.</t>
+          <t>pol.% (n)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SDom</t>
+          <t>sem. (n)</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Res %</t>
+          <t>pol.% (n)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Pol %</t>
+          <t>sem. (n)</t>
         </is>
       </c>
     </row>
@@ -505,42 +513,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>No Poverty</t>
+          <t>4.5 (288)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.415 (1,689)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>1.1 (1)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+0.007</t>
+          <t>0.443 (357)</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>5.9 (250)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>0.415 (1,191)</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1.8 (37)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5.3</t>
+          <t>0.556 (141)</t>
         </is>
       </c>
     </row>
@@ -552,42 +560,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Zero Hunger</t>
+          <t>4.3 (274)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>0.299 (1,508)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.020</t>
+          <t>0.0 (0)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+0.017</t>
+          <t>0.345 (240)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>5.8 (246)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>0.294 (1,196)</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.4 (28)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>0.454 (72)</t>
         </is>
       </c>
     </row>
@@ -599,42 +607,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Good Health</t>
+          <t>4.7 (298)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>0.495 (2,408)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>6.4 (6)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>+0.012</t>
+          <t>0.362 (643)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>22.3</t>
+          <t>6.7 (284)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+22.3</t>
+          <t>0.554 (1,707)</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>0.4 (8)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>0.695 (58)</t>
         </is>
       </c>
     </row>
@@ -646,42 +654,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Education</t>
+          <t>4.8 (305)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>0.267 (2,055)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.0 (0)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>+0.004</t>
+          <t>0.205 (274)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12.8</t>
+          <t>7.0 (296)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+12.8</t>
+          <t>0.287 (1,718)</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>0.4 (9)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>0.395 (63)</t>
         </is>
       </c>
     </row>
@@ -693,42 +701,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gender Equality</t>
+          <t>5.1 (324)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.278 (2,005)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>0.0 (0)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-0.022</t>
+          <t>0.276 (272)</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3.9</t>
+          <t>6.6 (278)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>0.282 (1,531)</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.2 (46)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>0.411 (202)</t>
         </is>
       </c>
     </row>
@@ -740,42 +748,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Clean Water</t>
+          <t>3.7 (238)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0.292 (1,206)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>0.0 (0)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>+0.017</t>
+          <t>0.346 (137)</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.3 (226)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>0.292 (1,038)</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.6 (12)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>0.422 (31)</t>
         </is>
       </c>
     </row>
@@ -787,42 +795,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>4.3 (273)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>0.427 (1,578)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>1.1 (1)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>0.511 (358)</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>6.0 (253)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.409 (1,147)</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>0.9 (19)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>0.591 (73)</t>
         </is>
       </c>
     </row>
@@ -834,42 +842,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Decent Work</t>
+          <t>4.3 (276)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>0.387 (1,886)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.030</t>
+          <t>0.0 (0)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>+0.004</t>
+          <t>0.395 (309)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>6.5 (275)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-3.7</t>
+          <t>0.397 (1,558)</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.0 (1)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>0.536 (19)</t>
         </is>
       </c>
     </row>
@@ -881,42 +889,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Innovation</t>
+          <t>4.3 (274)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>0.315 (2,986)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>50.0 (47)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>+0.010</t>
+          <t>0.272 (1,838)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>5.1 (215)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+17.6</t>
+          <t>0.545 (1,116)</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>0.6 (12)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.8</t>
+          <t>0.459 (32)</t>
         </is>
       </c>
     </row>
@@ -928,42 +936,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reduced Ineq.</t>
+          <t>2.9 (182)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>0.272 (1,085)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>0.0 (0)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>+0.004</t>
+          <t>0.331 (258)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>4.2 (176)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.6</t>
+          <t>0.278 (774)</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.3 (6)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>0.402 (53)</t>
         </is>
       </c>
     </row>
@@ -975,42 +983,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Sust. Cities</t>
+          <t>5.3 (338)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>0.449 (1,658)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.0 (0)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-0.001</t>
+          <t>0.428 (175)</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>8.0 (336)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-1.8</t>
+          <t>0.456 (1,474)</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>0.1 (2)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>0.573 (9)</t>
         </is>
       </c>
     </row>
@@ -1022,42 +1030,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Consumption</t>
+          <t>3.5 (226)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.296 (1,132)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>0.0 (0)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>+0.014</t>
+          <t>0.384 (178)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>5.3 (225)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-2.5</t>
+          <t>0.297 (947)</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.0 (1)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.5</t>
+          <t>0.488 (7)</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1077,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Climate</t>
+          <t>11.3 (718)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>0.480 (3,084)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>7.4 (7)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-0.003</t>
+          <t>0.437 (613)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>6.0 (252)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-5.9</t>
+          <t>0.444 (1,268)</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>22.4 (459)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>9.9</t>
+          <t>0.576 (1,203)</t>
         </is>
       </c>
     </row>
@@ -1116,42 +1124,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Life Below Water</t>
+          <t>3.8 (241)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>0.360 (1,293)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>0.0 (0)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>+0.005</t>
+          <t>0.372 (216)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>4.5 (189)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>0.354 (856)</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>2.5 (52)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>0.487 (221)</t>
         </is>
       </c>
     </row>
@@ -1163,42 +1171,42 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Life on Land</t>
+          <t>4.2 (266)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>0.238 (1,484)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.0 (0)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>+0.012</t>
+          <t>0.289 (299)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>5.7 (239)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.237 (1,108)</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>1.3 (27)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4.1</t>
+          <t>0.409 (77)</t>
         </is>
       </c>
     </row>
@@ -1210,42 +1218,42 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Peace &amp; Justice</t>
+          <t>17.3 (1,100)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.040</t>
+          <t>0.329 (4,890)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>12.8 (12)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-0.037</t>
+          <t>0.195 (1,092)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>5.9 (250)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-9.1</t>
+          <t>0.377 (1,395)</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>11.6</t>
+          <t>40.9 (838)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>0.506 (2,403)</t>
         </is>
       </c>
     </row>
@@ -1257,89 +1265,89 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Partnerships</t>
+          <t>11.7 (746)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>0.177 (3,645)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>21.3 (20)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-0.019</t>
+          <t>0.181 (859)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>9.1</t>
+          <t>5.6 (235)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-9.1</t>
+          <t>0.165 (1,322)</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>24.0 (491)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>0.260 (1,464)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Mean</t>
+          <t>ρ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>0.355</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>+0.002</t>
+          <t>0.733</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6.2</t>
+          <t>0.613</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+0.0</t>
+          <t>0.914</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>0.453</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>0.966</t>
         </is>
       </c>
     </row>
